--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,7 +460,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B2" t="n">
         <v>322</v>
@@ -472,7 +472,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,7 +492,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
         <v>322</v>
@@ -504,7 +504,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,103 +524,103 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>302</v>
+        <v>376</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>302</v>
+        <v>376</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>376</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
         <v>302</v>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
@@ -664,44 +664,48 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ppo28</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -712,63 +716,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LilianeB</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -740,7 +740,11 @@
           <t>Ppo28</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -768,7 +772,11 @@
           <t>MatuRenard</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>322</v>
+        <v>405</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,19 +492,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,33 +652,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>365</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>21</v>
       </c>
       <c r="B10" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -751,16 +751,16 @@
         <v>19</v>
       </c>
       <c r="B11" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,45 +460,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B2" t="n">
-        <v>405</v>
+        <v>322</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -508,17 +508,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,10 +527,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -540,17 +540,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,10 +559,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -572,17 +572,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,10 +591,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -604,26 +604,26 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -636,29 +636,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B8" t="n">
-        <v>365</v>
+        <v>259</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -668,29 +668,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B9" t="n">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -700,29 +700,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -732,29 +732,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,42 +460,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>322</v>
+        <v>440</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -504,94 +504,94 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>376</v>
+        <v>444</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B5" t="n">
-        <v>376</v>
+        <v>322</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>400</v>
+        <v>497</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -600,30 +600,30 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -632,144 +632,144 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>259</v>
+        <v>402</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>259</v>
+        <v>402</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>280</v>
+        <v>381</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,190 +495,190 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>322</v>
+        <v>496</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B6" t="n">
-        <v>497</v>
+        <v>366</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>402</v>
+        <v>485</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>402</v>
+        <v>446</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,30 +719,30 @@
         <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>376</v>
+        <v>425</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,42 +524,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>440</v>
+        <v>511</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>496</v>
+        <v>416</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -568,80 +568,80 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B6" t="n">
-        <v>366</v>
+        <v>440</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -652,65 +652,65 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>446</v>
+        <v>500</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,62 +719,62 @@
         <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>601</v>
+        <v>903</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,179 +492,179 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>503</v>
+        <v>710</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>511</v>
+        <v>726</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>416</v>
+        <v>668</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>440</v>
+        <v>691</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>645</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>455</v>
+        <v>665</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -684,28 +684,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -716,28 +716,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B10" t="n">
-        <v>435</v>
+        <v>488</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,33 +748,33 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B11" t="n">
-        <v>440</v>
+        <v>524</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,7 +460,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
         <v>903</v>
@@ -472,7 +472,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,10 +492,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>710</v>
+        <v>668</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
@@ -504,30 +504,30 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>726</v>
+        <v>691</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
@@ -536,30 +536,30 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>668</v>
+        <v>710</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
@@ -568,21 +568,21 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>691</v>
+        <v>726</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
@@ -600,21 +600,21 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
@@ -632,48 +632,48 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>665</v>
+        <v>524</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,97 +684,97 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
-        <v>474</v>
+        <v>568</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>488</v>
+        <v>555</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
-        <v>524</v>
+        <v>601</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,28 +460,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B2" t="n">
-        <v>903</v>
+        <v>813</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -492,289 +492,289 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>668</v>
+        <v>833</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>876</v>
+      </c>
+      <c r="C4" t="n">
         <v>9</v>
       </c>
-      <c r="B4" t="n">
-        <v>691</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
-      </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>710</v>
+        <v>892</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>726</v>
+        <v>915</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B7" t="n">
-        <v>665</v>
+        <v>616</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>524</v>
+        <v>1154</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>568</v>
+        <v>1004</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>555</v>
+        <v>839</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>601</v>
+        <v>796</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,51 +460,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C2" t="n">
         <v>11</v>
       </c>
-      <c r="B2" t="n">
-        <v>813</v>
-      </c>
-      <c r="C2" t="n">
-        <v>9</v>
-      </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3" t="n">
+        <v>879</v>
+      </c>
+      <c r="C3" t="n">
         <v>10</v>
       </c>
-      <c r="B3" t="n">
-        <v>833</v>
-      </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>876</v>
+        <v>915</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>892</v>
+        <v>922</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,89 +591,89 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>915</v>
+        <v>938</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>616</v>
+        <v>859</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B8" t="n">
-        <v>1154</v>
+        <v>669</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,60 +684,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
-        <v>1004</v>
+        <v>721</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>839</v>
+        <v>741</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,28 +748,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B11" t="n">
-        <v>796</v>
+        <v>616</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,60 +460,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>1080</v>
+        <v>1220</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>879</v>
+        <v>1190</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -524,97 +524,97 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>915</v>
+        <v>1011</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>922</v>
+        <v>956</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>938</v>
+        <v>1427</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -623,158 +623,158 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>859</v>
+        <v>1125</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B8" t="n">
-        <v>669</v>
+        <v>886</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>721</v>
+        <v>1148</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>741</v>
+        <v>1347</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>616</v>
+        <v>1058</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,318 +463,318 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>1220</v>
+        <v>1335</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>1190</v>
+        <v>1356</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1011</v>
+        <v>1204</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>956</v>
+        <v>1204</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>1427</v>
+        <v>1333</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B7" t="n">
-        <v>1125</v>
+        <v>970</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
-        <v>886</v>
+        <v>1080</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>1148</v>
+        <v>1234</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1347</v>
+        <v>1244</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>1058</v>
+        <v>1162</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,124 +460,124 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B2" t="n">
-        <v>1335</v>
+        <v>1261</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>1356</v>
+        <v>1302</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>1204</v>
+        <v>1574</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>1204</v>
+        <v>1533</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -588,156 +588,156 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>1333</v>
+        <v>1667</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>970</v>
+        <v>1448</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>1080</v>
+        <v>1445</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>1244</v>
+        <v>1321</v>
       </c>
       <c r="C10" t="n">
         <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,28 +748,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>1162</v>
+        <v>1412</v>
       </c>
       <c r="C11" t="n">
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,60 +460,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>1261</v>
+        <v>1751</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1302</v>
+        <v>1671</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -524,97 +524,97 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B4" t="n">
-        <v>1574</v>
+        <v>1366</v>
       </c>
       <c r="C4" t="n">
         <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B5" t="n">
-        <v>1533</v>
+        <v>1354</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
-        <v>1667</v>
+        <v>1498</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,89 +623,89 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>1448</v>
+        <v>1638</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
-        <v>1445</v>
+        <v>1503</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="n">
-        <v>1229</v>
+        <v>1388</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -716,28 +716,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B10" t="n">
-        <v>1321</v>
+        <v>1372</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,33 +748,33 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>1412</v>
+        <v>1577</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,51 +460,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B2" t="n">
-        <v>1751</v>
+        <v>1615</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>1671</v>
+        <v>1761</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,60 +524,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
-        <v>1366</v>
+        <v>1666</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>1354</v>
+        <v>1841</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -588,28 +588,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
-        <v>1498</v>
+        <v>1444</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -620,92 +620,92 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1638</v>
+        <v>1781</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B8" t="n">
-        <v>1503</v>
+        <v>1587</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B9" t="n">
-        <v>1388</v>
+        <v>1481</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -716,28 +716,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
-        <v>1372</v>
+        <v>1667</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,28 +748,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>1577</v>
+        <v>1734</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,92 +460,92 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1932</v>
+      </c>
+      <c r="C2" t="n">
         <v>27</v>
       </c>
-      <c r="B2" t="n">
-        <v>1615</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21</v>
-      </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>1761</v>
+        <v>2026</v>
       </c>
       <c r="C3" t="n">
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1666</v>
+        <v>2007</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -556,19 +556,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
-        <v>1841</v>
-      </c>
-      <c r="C5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7</v>
-      </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,156 +588,156 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>1444</v>
+        <v>2155</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>1781</v>
+        <v>1869</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
-        <v>1587</v>
+        <v>1768</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>1481</v>
+        <v>2125</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" t="n">
-        <v>1667</v>
+        <v>1769</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,33 +748,33 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>1734</v>
+        <v>1886</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,10 +460,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>1932</v>
+        <v>1955</v>
       </c>
       <c r="C2" t="n">
         <v>27</v>
@@ -472,80 +472,80 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>2026</v>
+        <v>1992</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>2007</v>
+        <v>2147</v>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -556,28 +556,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>2010</v>
+        <v>2144</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -588,19 +588,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>2155</v>
+        <v>2292</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -620,161 +620,161 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>1869</v>
+        <v>2163</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1929</v>
+      </c>
+      <c r="C8" t="n">
         <v>27</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1768</v>
-      </c>
-      <c r="C8" t="n">
-        <v>24</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2125</v>
+        <v>2179</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>1769</v>
+        <v>2185</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>1886</v>
+        <v>2040</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,92 +460,92 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>1955</v>
+        <v>2499</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1992</v>
+        <v>2635</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2338</v>
+      </c>
+      <c r="C4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D4" t="n">
         <v>9</v>
       </c>
-      <c r="B4" t="n">
-        <v>2147</v>
-      </c>
-      <c r="C4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -556,83 +556,83 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>2144</v>
+        <v>2210</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>2292</v>
+        <v>2402</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>2163</v>
+        <v>2298</v>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,129 +652,129 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B8" t="n">
-        <v>1929</v>
+        <v>2104</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
-        <v>2179</v>
+        <v>2161</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>2185</v>
+        <v>2347</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>2040</v>
+        <v>2431</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,92 +460,92 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2499</v>
+        <v>2892</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>2635</v>
+        <v>2581</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>2338</v>
+        <v>2608</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -556,19 +556,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
-        <v>2210</v>
+        <v>2443</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,19 +588,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2531</v>
+      </c>
+      <c r="C6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D6" t="n">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
-        <v>2402</v>
-      </c>
-      <c r="C6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -620,60 +620,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B7" t="n">
-        <v>2298</v>
+        <v>2286</v>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B8" t="n">
-        <v>2104</v>
+        <v>2312</v>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,92 +684,92 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>2161</v>
+        <v>2447</v>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B10" t="n">
-        <v>2347</v>
+        <v>2374</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>2431</v>
+        <v>2789</v>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>2892</v>
+        <v>3103</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,60 +492,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>2581</v>
+        <v>2819</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>2608</v>
+        <v>2754</v>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -556,19 +556,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>2443</v>
+        <v>2777</v>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,60 +588,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>2531</v>
+        <v>2792</v>
       </c>
       <c r="C6" t="n">
         <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2797</v>
+      </c>
+      <c r="C7" t="n">
         <v>41</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2286</v>
-      </c>
-      <c r="C7" t="n">
-        <v>32</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -652,28 +652,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2734</v>
+      </c>
+      <c r="C8" t="n">
         <v>38</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2312</v>
-      </c>
-      <c r="C8" t="n">
-        <v>35</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,28 +684,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B9" t="n">
-        <v>2447</v>
+        <v>2646</v>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -716,60 +716,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>56</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2378</v>
+      </c>
+      <c r="C10" t="n">
         <v>28</v>
       </c>
-      <c r="B10" t="n">
-        <v>2374</v>
-      </c>
-      <c r="C10" t="n">
-        <v>34</v>
-      </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="B11" t="n">
-        <v>2789</v>
+        <v>2134</v>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>3103</v>
+        <v>3357</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,25 +495,25 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>2819</v>
+        <v>3134</v>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -524,28 +524,28 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B4" t="n">
-        <v>2754</v>
+        <v>2880</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -556,156 +556,156 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>2777</v>
+        <v>2911</v>
       </c>
       <c r="C5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="n">
-        <v>2792</v>
+        <v>3094</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>2797</v>
+        <v>3048</v>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>2734</v>
+        <v>3021</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B9" t="n">
-        <v>2646</v>
+        <v>2912</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -716,65 +716,65 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
-        <v>2378</v>
+        <v>3025</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>2134</v>
+        <v>3061</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>3357</v>
+        <v>3421</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,48 +495,48 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>3134</v>
+        <v>3208</v>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="n">
-        <v>2880</v>
+        <v>2944</v>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,19 +556,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
-        <v>2911</v>
+        <v>2975</v>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,30 +591,30 @@
         <v>14</v>
       </c>
       <c r="B6" t="n">
-        <v>3094</v>
+        <v>3198</v>
       </c>
       <c r="C6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,16 +623,16 @@
         <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>3048</v>
+        <v>3112</v>
       </c>
       <c r="C7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,28 +652,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>3021</v>
+        <v>3431</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,97 +684,97 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>2912</v>
+        <v>3085</v>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B10" t="n">
-        <v>3025</v>
+        <v>2432</v>
       </c>
       <c r="C10" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>3061</v>
+        <v>3266</v>
       </c>
       <c r="C11" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>3421</v>
+        <v>3486</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,83 +492,83 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3163</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3" t="n">
         <v>13</v>
       </c>
-      <c r="B3" t="n">
-        <v>3208</v>
-      </c>
-      <c r="C3" t="n">
-        <v>45</v>
-      </c>
-      <c r="D3" t="n">
-        <v>12</v>
-      </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B4" t="n">
-        <v>2944</v>
+        <v>3293</v>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>2975</v>
+        <v>3174</v>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,193 +588,193 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>3198</v>
+        <v>3454</v>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
-        <v>3112</v>
+        <v>3263</v>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>3431</v>
+        <v>3197</v>
       </c>
       <c r="C8" t="n">
         <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
-        <v>3085</v>
+        <v>3170</v>
       </c>
       <c r="C9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="B10" t="n">
-        <v>2432</v>
+        <v>3003</v>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3266</v>
+        <v>3392</v>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>3486</v>
+        <v>3733</v>
       </c>
       <c r="C2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,92 +492,92 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>3163</v>
+        <v>3550</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>3293</v>
+        <v>3451</v>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B5" t="n">
-        <v>3174</v>
+        <v>3201</v>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -588,161 +588,161 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>3454</v>
+        <v>3510</v>
       </c>
       <c r="C6" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>3263</v>
+        <v>3417</v>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B8" t="n">
-        <v>3197</v>
+        <v>3210</v>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3170</v>
+        <v>3576</v>
       </c>
       <c r="C9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B10" t="n">
-        <v>3003</v>
+        <v>3319</v>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3392</v>
+        <v>3544</v>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>3733</v>
+        <v>3772</v>
       </c>
       <c r="C2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,19 +492,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>3550</v>
+        <v>3589</v>
       </c>
       <c r="C3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>3451</v>
+        <v>3490</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,28 +556,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>3201</v>
+        <v>3549</v>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" t="n">
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -588,28 +588,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B6" t="n">
-        <v>3510</v>
+        <v>3201</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -620,19 +620,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>3417</v>
+        <v>3456</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,19 +652,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" t="n">
-        <v>3210</v>
+        <v>3249</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -684,42 +684,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
-        <v>3576</v>
+        <v>3408</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>3319</v>
+        <v>3466</v>
       </c>
       <c r="C10" t="n">
         <v>50</v>
@@ -728,33 +728,33 @@
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>3544</v>
+        <v>3561</v>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>3772</v>
+        <v>3904</v>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,19 +492,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>3589</v>
+        <v>3721</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,19 +524,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>3490</v>
+        <v>3542</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,19 +556,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>3549</v>
+        <v>3601</v>
       </c>
       <c r="C5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" t="n">
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,28 +588,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B6" t="n">
-        <v>3201</v>
+        <v>3401</v>
       </c>
       <c r="C6" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -620,19 +620,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
-        <v>3456</v>
+        <v>3528</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,28 +652,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" t="n">
-        <v>3249</v>
+        <v>3253</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,83 +684,83 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>3408</v>
+        <v>3618</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>3466</v>
+        <v>3460</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>3561</v>
+        <v>3613</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>3904</v>
+        <v>4099</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,19 +492,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>3721</v>
+        <v>3896</v>
       </c>
       <c r="C3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,19 +524,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>3542</v>
+        <v>3644</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,28 +556,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>3601</v>
+        <v>3596</v>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -588,51 +588,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>3401</v>
+        <v>3843</v>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
-        <v>3528</v>
+        <v>3703</v>
       </c>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,28 +652,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>3253</v>
+        <v>3703</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,97 +684,97 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B9" t="n">
-        <v>3618</v>
+        <v>3428</v>
       </c>
       <c r="C9" t="n">
         <v>52</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>82</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
-        <v>3460</v>
+        <v>3255</v>
       </c>
       <c r="C10" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>3613</v>
+        <v>3249</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4099</v>
+        <v>4190</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,19 +492,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>3896</v>
+        <v>3987</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>3644</v>
+        <v>3735</v>
       </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,10 +556,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>3596</v>
+        <v>3868</v>
       </c>
       <c r="C5" t="n">
         <v>56</v>
@@ -568,71 +568,71 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B6" t="n">
-        <v>3843</v>
+        <v>3687</v>
       </c>
       <c r="C6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>3703</v>
+        <v>3819</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,28 +652,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B8" t="n">
-        <v>3703</v>
+        <v>3472</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,19 +684,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B9" t="n">
-        <v>3428</v>
+        <v>3569</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -716,28 +716,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>3255</v>
+        <v>3794</v>
       </c>
       <c r="C10" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,33 +748,33 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>3249</v>
+        <v>4018</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4190</v>
+        <v>4286</v>
       </c>
       <c r="C2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>3987</v>
+        <v>4083</v>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>3735</v>
+        <v>3831</v>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,19 +556,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="n">
-        <v>3868</v>
+        <v>3964</v>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,19 +588,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" t="n">
-        <v>3687</v>
+        <v>3783</v>
       </c>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>3819</v>
+        <v>3915</v>
       </c>
       <c r="C7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,19 +652,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="n">
-        <v>3472</v>
+        <v>3500</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>33</v>
       </c>
       <c r="B9" t="n">
-        <v>3569</v>
+        <v>3665</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>3794</v>
+        <v>3890</v>
       </c>
       <c r="C10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>4018</v>
+        <v>4114</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4286</v>
+        <v>4379</v>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,28 +492,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>4083</v>
+        <v>4065</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -524,156 +524,156 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>3831</v>
+        <v>4176</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B5" t="n">
-        <v>3964</v>
+        <v>3831</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>3783</v>
+        <v>3964</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
-        <v>3915</v>
+        <v>3783</v>
       </c>
       <c r="C7" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B8" t="n">
-        <v>3500</v>
+        <v>3665</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,28 +684,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B9" t="n">
-        <v>3665</v>
+        <v>3500</v>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -716,28 +716,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B10" t="n">
-        <v>3890</v>
+        <v>3617</v>
       </c>
       <c r="C10" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,7 +748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
         <v>4114</v>
@@ -760,7 +760,7 @@
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4379</v>
+        <v>4551</v>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,28 +492,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>4065</v>
+        <v>4248</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -524,28 +524,28 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B4" t="n">
-        <v>4176</v>
+        <v>4065</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -556,7 +556,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" t="n">
         <v>3831</v>
@@ -568,7 +568,7 @@
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,83 +588,83 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B6" t="n">
-        <v>3964</v>
+        <v>3855</v>
       </c>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
-        <v>3783</v>
+        <v>3964</v>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B8" t="n">
-        <v>3665</v>
+        <v>3737</v>
       </c>
       <c r="C8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>50</v>
       </c>
       <c r="B9" t="n">
-        <v>3500</v>
+        <v>3572</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -716,28 +716,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B10" t="n">
-        <v>3617</v>
+        <v>3890</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,19 +748,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>4114</v>
+        <v>4186</v>
       </c>
       <c r="C11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4551</v>
+        <v>4594</v>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>4248</v>
+        <v>4291</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,19 +524,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>4065</v>
+        <v>4108</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,19 +556,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
-        <v>3831</v>
+        <v>3874</v>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>27</v>
       </c>
       <c r="B6" t="n">
-        <v>3855</v>
+        <v>3898</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
-        <v>3964</v>
+        <v>4120</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,19 +652,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>3737</v>
+        <v>3893</v>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -684,19 +684,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B9" t="n">
-        <v>3572</v>
+        <v>3728</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -716,28 +716,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
-        <v>3890</v>
+        <v>3732</v>
       </c>
       <c r="C10" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,10 +748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B11" t="n">
-        <v>4186</v>
+        <v>3933</v>
       </c>
       <c r="C11" t="n">
         <v>60</v>
@@ -760,21 +760,21 @@
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4594</v>
+        <v>4648</v>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,19 +492,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>4291</v>
+        <v>4395</v>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,60 +524,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>4108</v>
+        <v>3928</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B5" t="n">
-        <v>3874</v>
+        <v>3997</v>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -588,92 +588,92 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B6" t="n">
-        <v>3898</v>
+        <v>4162</v>
       </c>
       <c r="C6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>4120</v>
+        <v>3952</v>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
-        <v>3893</v>
+        <v>3782</v>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -684,60 +684,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>3728</v>
+        <v>4174</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>3732</v>
+        <v>4193</v>
       </c>
       <c r="C10" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,28 +748,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
-        <v>3933</v>
+        <v>3786</v>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4648</v>
+        <v>4728</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,19 +492,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>4395</v>
+        <v>4475</v>
       </c>
       <c r="C3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,19 +524,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="n">
-        <v>3928</v>
+        <v>3988</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,19 +556,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>3997</v>
+        <v>4057</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" t="n">
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>17</v>
       </c>
       <c r="B6" t="n">
-        <v>4162</v>
+        <v>4222</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>3952</v>
+        <v>4012</v>
       </c>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,28 +652,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>3782</v>
+        <v>4013</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -687,16 +687,16 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>4174</v>
+        <v>4234</v>
       </c>
       <c r="C9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -716,60 +716,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3798</v>
+      </c>
+      <c r="C10" t="n">
+        <v>58</v>
+      </c>
+      <c r="D10" t="n">
         <v>14</v>
       </c>
-      <c r="B10" t="n">
-        <v>4193</v>
-      </c>
-      <c r="C10" t="n">
-        <v>59</v>
-      </c>
-      <c r="D10" t="n">
-        <v>13</v>
-      </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
-        <v>3786</v>
+        <v>3782</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4728</v>
+        <v>4889</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,19 +492,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>4475</v>
+        <v>4636</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,33 +524,33 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B4" t="n">
-        <v>3988</v>
+        <v>4336</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,16 +559,16 @@
         <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>4057</v>
+        <v>4121</v>
       </c>
       <c r="C5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,13 +588,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B6" t="n">
-        <v>4222</v>
+        <v>4110</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
         <v>15</v>
@@ -604,44 +604,44 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
-        <v>4012</v>
+        <v>4052</v>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -652,129 +652,129 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>4013</v>
+        <v>3912</v>
       </c>
       <c r="C8" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3879</v>
+      </c>
+      <c r="C9" t="n">
+        <v>56</v>
+      </c>
+      <c r="D9" t="n">
         <v>15</v>
       </c>
-      <c r="B9" t="n">
-        <v>4234</v>
-      </c>
-      <c r="C9" t="n">
-        <v>62</v>
-      </c>
-      <c r="D9" t="n">
-        <v>14</v>
-      </c>
       <c r="E9" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>3798</v>
+        <v>4555</v>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>3782</v>
+        <v>4298</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D11" t="n">
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -460,19 +460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4889</v>
+        <v>5004</v>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
         <v>4336</v>
@@ -536,7 +536,7 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="n">
         <v>4121</v>
@@ -568,7 +568,7 @@
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="n">
         <v>4052</v>
@@ -632,7 +632,7 @@
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" t="n">
         <v>4298</v>
@@ -760,7 +760,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -472,7 +472,7 @@
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,7 +492,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
         <v>4636</v>
@@ -504,7 +504,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,19 +524,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>4336</v>
+        <v>4465</v>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,92 +556,92 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B5" t="n">
-        <v>4121</v>
+        <v>4041</v>
       </c>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4110</v>
+        <v>4684</v>
       </c>
       <c r="C6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D6" t="n">
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B7" t="n">
-        <v>4052</v>
+        <v>4121</v>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" t="n">
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -652,60 +652,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B8" t="n">
-        <v>3912</v>
+        <v>4052</v>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" t="n">
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B9" t="n">
-        <v>3879</v>
+        <v>4110</v>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -716,65 +716,65 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>4555</v>
+        <v>3879</v>
       </c>
       <c r="C10" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B11" t="n">
-        <v>4298</v>
+        <v>4076</v>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D11" t="n">
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/snipers.xlsx
+++ b/snipers.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5004</v>
+        <v>5094</v>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>4636</v>
+        <v>4806</v>
       </c>
       <c r="C3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
         <v>4465</v>
@@ -536,7 +536,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,51 +556,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>4041</v>
+        <v>4261</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" t="n">
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4684</v>
+        <v>4904</v>
       </c>
       <c r="C6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -620,51 +620,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B7" t="n">
-        <v>4121</v>
+        <v>4041</v>
       </c>
       <c r="C7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
-        <v>4052</v>
+        <v>4222</v>
       </c>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D8" t="n">
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -684,28 +684,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B9" t="n">
-        <v>4110</v>
+        <v>4039</v>
       </c>
       <c r="C9" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -716,28 +716,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>3879</v>
+        <v>4190</v>
       </c>
       <c r="C10" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
         <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -748,33 +748,33 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
-        <v>4076</v>
+        <v>4298</v>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" t="n">
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
